--- a/ExcelOutputs/triggers.xlsx
+++ b/ExcelOutputs/triggers.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angus\OneDrive\Documents\repos\TCGsims\ExcelOutputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C43B24B-157D-4534-96B2-8334382E062E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CB3734-47A0-4DD2-A4F3-0098A92244C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="No triggers, Twin Drive" sheetId="1" r:id="rId1"/>
-    <sheet name="Total going 1st" sheetId="2" r:id="rId2"/>
-    <sheet name="Total going 2nd" sheetId="3" r:id="rId3"/>
-    <sheet name="Twin Drive" sheetId="4" r:id="rId4"/>
-    <sheet name="Triple Drive" sheetId="5" r:id="rId5"/>
+    <sheet name="Twin Drive" sheetId="1" r:id="rId1"/>
+    <sheet name="2D Keep one" sheetId="2" r:id="rId2"/>
+    <sheet name="Triple Drive" sheetId="4" r:id="rId3"/>
+    <sheet name="3D Keep one" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="12">
   <si>
     <t>Critical</t>
   </si>
@@ -50,12 +49,36 @@
   <si>
     <t>n</t>
   </si>
+  <si>
+    <t>Score is the probability of at least one trigger seen in drive or damage checks</t>
+  </si>
+  <si>
+    <t>Probability of seeing critical trigger with Triple Drive, but one critical is kept in hand during opening mulligan</t>
+  </si>
+  <si>
+    <t>Vanguard only has Twin Drive</t>
+  </si>
+  <si>
+    <t>Vanguard gets Triple Drive when opponent is at grade 3</t>
+  </si>
+  <si>
+    <t>Probability of seeing critical trigger with Twin Drive, but one critical is kept in hand during opening mulligan</t>
+  </si>
+  <si>
+    <t>Drawn</t>
+  </si>
+  <si>
+    <t>In Drive</t>
+  </si>
+  <si>
+    <t>In Damage</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,6 +100,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -141,10 +171,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -155,9 +186,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -457,31 +490,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3">
-        <v>0</v>
-      </c>
-      <c r="G1" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2">
@@ -490,25 +529,24 @@
       <c r="C2">
         <v>8</v>
       </c>
-      <c r="D2">
-        <v>0.77490000000000003</v>
+      <c r="D2" s="4">
+        <v>0.92979999999999996</v>
       </c>
       <c r="E2">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F2">
-        <v>1.2606999999999999</v>
+        <v>1.2598</v>
       </c>
       <c r="G2">
-        <v>0.84179999999999999</v>
-      </c>
-      <c r="I2">
-        <f>D2-D3</f>
-        <v>5.259999999999998E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+        <v>0.84089999999999998</v>
+      </c>
+      <c r="H2">
+        <v>1.5345</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3">
@@ -517,25 +555,24 @@
       <c r="C3">
         <v>9</v>
       </c>
-      <c r="D3">
-        <v>0.72230000000000005</v>
+      <c r="D3" s="4">
+        <v>0.89949999999999997</v>
       </c>
       <c r="E3">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F3">
-        <v>1.0982000000000001</v>
+        <v>1.0945</v>
       </c>
       <c r="G3">
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I10" si="0">D3-D4</f>
-        <v>6.0600000000000098E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+        <v>0.73780000000000001</v>
+      </c>
+      <c r="H3">
+        <v>1.3465</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4">
@@ -544,25 +581,24 @@
       <c r="C4">
         <v>10</v>
       </c>
-      <c r="D4">
-        <v>0.66169999999999995</v>
+      <c r="D4" s="4">
+        <v>0.85760000000000003</v>
       </c>
       <c r="E4">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F4">
-        <v>0.94089999999999996</v>
+        <v>0.94679999999999997</v>
       </c>
       <c r="G4">
-        <v>0.63049999999999995</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="0"/>
-        <v>6.8899999999999961E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+        <v>0.62939999999999996</v>
+      </c>
+      <c r="H4">
+        <v>1.1513</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5">
@@ -571,25 +607,24 @@
       <c r="C5">
         <v>11</v>
       </c>
-      <c r="D5">
-        <v>0.59279999999999999</v>
+      <c r="D5" s="4">
+        <v>0.7994</v>
       </c>
       <c r="E5">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F5">
-        <v>0.78759999999999997</v>
+        <v>0.78739999999999999</v>
       </c>
       <c r="G5">
-        <v>0.52669999999999995</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="0"/>
-        <v>8.3699999999999997E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+        <v>0.52649999999999997</v>
+      </c>
+      <c r="H5">
+        <v>0.96189999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6">
@@ -598,25 +633,24 @@
       <c r="C6">
         <v>12</v>
       </c>
-      <c r="D6">
-        <v>0.5091</v>
+      <c r="D6" s="4">
+        <v>0.71750000000000003</v>
       </c>
       <c r="E6">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F6">
-        <v>0.63019999999999998</v>
+        <v>0.63070000000000004</v>
       </c>
       <c r="G6">
-        <v>0.4204</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="0"/>
-        <v>9.9499999999999977E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
+        <v>0.41860000000000003</v>
+      </c>
+      <c r="H6">
+        <v>0.76880000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7">
@@ -625,25 +659,24 @@
       <c r="C7">
         <v>13</v>
       </c>
-      <c r="D7">
-        <v>0.40960000000000002</v>
+      <c r="D7" s="4">
+        <v>0.60960000000000003</v>
       </c>
       <c r="E7">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F7">
-        <v>0.47360000000000002</v>
+        <v>0.4718</v>
       </c>
       <c r="G7">
-        <v>0.31580000000000003</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="0"/>
-        <v>0.11780000000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+        <v>0.31780000000000003</v>
+      </c>
+      <c r="H7">
+        <v>0.57830000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8">
@@ -652,25 +685,24 @@
       <c r="C8">
         <v>14</v>
       </c>
-      <c r="D8">
-        <v>0.2918</v>
+      <c r="D8" s="4">
+        <v>0.4592</v>
       </c>
       <c r="E8">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F8">
-        <v>0.3135</v>
+        <v>0.31390000000000001</v>
       </c>
       <c r="G8">
-        <v>0.21079999999999999</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="0"/>
-        <v>0.13289999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
+        <v>0.21149999999999999</v>
+      </c>
+      <c r="H8">
+        <v>0.38450000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9">
@@ -679,25 +711,24 @@
       <c r="C9">
         <v>15</v>
       </c>
-      <c r="D9">
-        <v>0.15890000000000001</v>
+      <c r="D9" s="4">
+        <v>0.26019999999999999</v>
       </c>
       <c r="E9">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F9">
-        <v>0.15890000000000001</v>
+        <v>0.1573</v>
       </c>
       <c r="G9">
-        <v>0.10489999999999999</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="0"/>
-        <v>0.15890000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
+        <v>0.10290000000000001</v>
+      </c>
+      <c r="H9">
+        <v>0.19159999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10">
@@ -706,11 +737,11 @@
       <c r="C10">
         <v>16</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -718,9 +749,18 @@
       <c r="G10">
         <v>0</v>
       </c>
-      <c r="I10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -730,44 +770,272 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1">
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.91890000000000005</v>
+      </c>
+      <c r="E2">
+        <v>100000</v>
+      </c>
+      <c r="F2">
+        <v>1.1968000000000001</v>
+      </c>
+      <c r="G2">
+        <v>0.7984</v>
+      </c>
+      <c r="H2">
+        <v>1.8531</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2">
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.8831</v>
+      </c>
+      <c r="E3">
+        <v>100000</v>
+      </c>
+      <c r="F3">
+        <v>1.0387999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0.69320000000000004</v>
+      </c>
+      <c r="H3">
+        <v>1.6418999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.83760000000000001</v>
+      </c>
+      <c r="E4">
+        <v>100000</v>
+      </c>
+      <c r="F4">
+        <v>0.89100000000000001</v>
+      </c>
+      <c r="G4">
+        <v>0.59550000000000003</v>
+      </c>
+      <c r="H4">
+        <v>1.4206000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.77659999999999996</v>
+      </c>
+      <c r="E5">
+        <v>100000</v>
+      </c>
+      <c r="F5">
+        <v>0.74160000000000004</v>
+      </c>
+      <c r="G5">
+        <v>0.497</v>
+      </c>
+      <c r="H5">
+        <v>1.1916</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.69069999999999998</v>
+      </c>
+      <c r="E6">
+        <v>100000</v>
+      </c>
+      <c r="F6">
+        <v>0.59079999999999999</v>
+      </c>
+      <c r="G6">
+        <v>0.3952</v>
+      </c>
+      <c r="H6">
+        <v>0.96340000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.58030000000000004</v>
+      </c>
+      <c r="E7">
+        <v>100000</v>
+      </c>
+      <c r="F7">
+        <v>0.44330000000000003</v>
+      </c>
+      <c r="G7">
+        <v>0.29480000000000001</v>
+      </c>
+      <c r="H7">
+        <v>0.72789999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.4355</v>
+      </c>
+      <c r="E8">
+        <v>100000</v>
+      </c>
+      <c r="F8">
+        <v>0.29330000000000001</v>
+      </c>
+      <c r="G8">
+        <v>0.1981</v>
+      </c>
+      <c r="H8">
+        <v>0.4894</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.24490000000000001</v>
+      </c>
+      <c r="E9">
+        <v>100000</v>
+      </c>
+      <c r="F9">
+        <v>0.14879999999999999</v>
+      </c>
+      <c r="G9">
+        <v>9.6100000000000005E-2</v>
+      </c>
+      <c r="H9">
+        <v>0.24660000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>16</v>
       </c>
-      <c r="C2">
-        <v>4.0263999999999998</v>
-      </c>
-      <c r="D2">
-        <v>200000</v>
-      </c>
-      <c r="E2">
-        <v>2.3498000000000001</v>
-      </c>
-      <c r="F2">
-        <v>1.6766000000000001</v>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>100000</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -776,45 +1044,278 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1">
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="E2">
+        <v>100000</v>
+      </c>
+      <c r="F2">
+        <v>1.6821999999999999</v>
+      </c>
+      <c r="G2">
+        <v>0.84319999999999995</v>
+      </c>
+      <c r="H2">
+        <v>1.5468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2">
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.94189999999999996</v>
+      </c>
+      <c r="E3">
+        <v>100000</v>
+      </c>
+      <c r="F3">
+        <v>1.4648000000000001</v>
+      </c>
+      <c r="G3">
+        <v>0.73760000000000003</v>
+      </c>
+      <c r="H3">
+        <v>1.3536999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.91159999999999997</v>
+      </c>
+      <c r="E4">
+        <v>100000</v>
+      </c>
+      <c r="F4">
+        <v>1.2605</v>
+      </c>
+      <c r="G4">
+        <v>0.62780000000000002</v>
+      </c>
+      <c r="H4">
+        <v>1.1604000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.86319999999999997</v>
+      </c>
+      <c r="E5">
+        <v>100000</v>
+      </c>
+      <c r="F5">
+        <v>1.0522</v>
+      </c>
+      <c r="G5">
+        <v>0.52539999999999998</v>
+      </c>
+      <c r="H5">
+        <v>0.9617</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.79100000000000004</v>
+      </c>
+      <c r="E6">
+        <v>100000</v>
+      </c>
+      <c r="F6">
+        <v>0.83819999999999995</v>
+      </c>
+      <c r="G6">
+        <v>0.41949999999999998</v>
+      </c>
+      <c r="H6">
+        <v>0.77710000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.68520000000000003</v>
+      </c>
+      <c r="E7">
+        <v>100000</v>
+      </c>
+      <c r="F7">
+        <v>0.62829999999999997</v>
+      </c>
+      <c r="G7">
+        <v>0.31409999999999999</v>
+      </c>
+      <c r="H7">
+        <v>0.57920000000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.53490000000000004</v>
+      </c>
+      <c r="E8">
+        <v>100000</v>
+      </c>
+      <c r="F8">
+        <v>0.4224</v>
+      </c>
+      <c r="G8">
+        <v>0.20810000000000001</v>
+      </c>
+      <c r="H8">
+        <v>0.38519999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.31230000000000002</v>
+      </c>
+      <c r="E9">
+        <v>100000</v>
+      </c>
+      <c r="F9">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="G9">
+        <v>0.1033</v>
+      </c>
+      <c r="H9">
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>16</v>
       </c>
-      <c r="C2">
-        <v>4.3616000000000001</v>
-      </c>
-      <c r="D2">
-        <v>200000</v>
-      </c>
-      <c r="E2">
-        <v>2.6861000000000002</v>
-      </c>
-      <c r="F2">
-        <v>1.6756</v>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>100000</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -823,32 +1324,38 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1">
-        <v>0</v>
-      </c>
-      <c r="G1" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
         <v>0</v>
       </c>
       <c r="B2">
@@ -857,21 +1364,24 @@
       <c r="C2">
         <v>8</v>
       </c>
-      <c r="D2">
-        <v>2.1006</v>
+      <c r="D2" s="4">
+        <v>0.95489999999999997</v>
       </c>
       <c r="E2">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F2">
-        <v>1.2622</v>
+        <v>1.5939000000000001</v>
       </c>
       <c r="G2">
-        <v>0.83840000000000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+        <v>0.79669999999999996</v>
+      </c>
+      <c r="H2">
+        <v>1.8704000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3">
@@ -880,21 +1390,24 @@
       <c r="C3">
         <v>9</v>
       </c>
-      <c r="D3">
-        <v>1.8379000000000001</v>
+      <c r="D3" s="4">
+        <v>0.92930000000000001</v>
       </c>
       <c r="E3">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F3">
-        <v>1.1048</v>
+        <v>1.3907</v>
       </c>
       <c r="G3">
-        <v>0.73309999999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+        <v>0.69640000000000002</v>
+      </c>
+      <c r="H3">
+        <v>1.6500999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4">
@@ -903,21 +1416,24 @@
       <c r="C4">
         <v>10</v>
       </c>
-      <c r="D4">
-        <v>1.5781000000000001</v>
+      <c r="D4" s="4">
+        <v>0.89359999999999995</v>
       </c>
       <c r="E4">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F4">
-        <v>0.94550000000000001</v>
+        <v>1.1895</v>
       </c>
       <c r="G4">
-        <v>0.63270000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+        <v>0.59340000000000004</v>
+      </c>
+      <c r="H4">
+        <v>1.4291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5">
@@ -926,21 +1442,24 @@
       <c r="C5">
         <v>11</v>
       </c>
-      <c r="D5">
-        <v>1.3129</v>
+      <c r="D5" s="4">
+        <v>0.84260000000000002</v>
       </c>
       <c r="E5">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F5">
-        <v>0.78549999999999998</v>
+        <v>0.9929</v>
       </c>
       <c r="G5">
-        <v>0.52739999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+        <v>0.49609999999999999</v>
+      </c>
+      <c r="H5">
+        <v>1.1952</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6">
@@ -949,21 +1468,24 @@
       <c r="C6">
         <v>12</v>
       </c>
-      <c r="D6">
-        <v>1.0519000000000001</v>
+      <c r="D6" s="4">
+        <v>0.76539999999999997</v>
       </c>
       <c r="E6">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F6">
-        <v>0.63039999999999996</v>
+        <v>0.78380000000000005</v>
       </c>
       <c r="G6">
-        <v>0.42149999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+        <v>0.3972</v>
+      </c>
+      <c r="H6">
+        <v>0.96279999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7">
@@ -972,21 +1494,24 @@
       <c r="C7">
         <v>13</v>
       </c>
-      <c r="D7">
-        <v>0.79139999999999999</v>
+      <c r="D7" s="4">
+        <v>0.66010000000000002</v>
       </c>
       <c r="E7">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F7">
-        <v>0.4753</v>
+        <v>0.59279999999999999</v>
       </c>
       <c r="G7">
-        <v>0.31609999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+        <v>0.29520000000000002</v>
+      </c>
+      <c r="H7">
+        <v>0.72929999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8">
@@ -995,21 +1520,24 @@
       <c r="C8">
         <v>14</v>
       </c>
-      <c r="D8">
-        <v>0.52710000000000001</v>
+      <c r="D8" s="4">
+        <v>0.50439999999999996</v>
       </c>
       <c r="E8">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F8">
-        <v>0.31759999999999999</v>
+        <v>0.39019999999999999</v>
       </c>
       <c r="G8">
-        <v>0.2094</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+        <v>0.1956</v>
+      </c>
+      <c r="H8">
+        <v>0.4929</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9">
@@ -1018,21 +1546,24 @@
       <c r="C9">
         <v>15</v>
       </c>
-      <c r="D9">
-        <v>0.26</v>
+      <c r="D9" s="4">
+        <v>0.29360000000000003</v>
       </c>
       <c r="E9">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F9">
-        <v>0.15579999999999999</v>
+        <v>0.19450000000000001</v>
       </c>
       <c r="G9">
-        <v>0.1041</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="H9">
+        <v>0.24859999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10">
@@ -1041,11 +1572,11 @@
       <c r="C10">
         <v>16</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1053,242 +1584,13 @@
       <c r="G10">
         <v>0</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2">
-        <v>0</v>
-      </c>
-      <c r="G1" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2">
-        <v>2.6008</v>
-      </c>
-      <c r="E2">
-        <v>200000</v>
-      </c>
-      <c r="F2">
-        <v>1.7599</v>
-      </c>
-      <c r="G2">
-        <v>0.84099999999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>2.2759999999999998</v>
-      </c>
-      <c r="E3">
-        <v>200000</v>
-      </c>
-      <c r="F3">
-        <v>1.5399</v>
-      </c>
-      <c r="G3">
-        <v>0.73599999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>1.9504999999999999</v>
-      </c>
-      <c r="E4">
-        <v>200000</v>
-      </c>
-      <c r="F4">
-        <v>1.3227</v>
-      </c>
-      <c r="G4">
-        <v>0.62770000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5">
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>5</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>1.6278999999999999</v>
-      </c>
-      <c r="E5">
-        <v>200000</v>
-      </c>
-      <c r="F5">
-        <v>1.1016999999999999</v>
-      </c>
-      <c r="G5">
-        <v>0.5262</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>1.3016000000000001</v>
-      </c>
-      <c r="E6">
-        <v>200000</v>
-      </c>
-      <c r="F6">
-        <v>0.88390000000000002</v>
-      </c>
-      <c r="G6">
-        <v>0.41770000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>13</v>
-      </c>
-      <c r="D7">
-        <v>0.97289999999999999</v>
-      </c>
-      <c r="E7">
-        <v>200000</v>
-      </c>
-      <c r="F7">
-        <v>0.65900000000000003</v>
-      </c>
-      <c r="G7">
-        <v>0.314</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>14</v>
-      </c>
-      <c r="D8">
-        <v>0.64949999999999997</v>
-      </c>
-      <c r="E8">
-        <v>200000</v>
-      </c>
-      <c r="F8">
-        <v>0.44019999999999998</v>
-      </c>
-      <c r="G8">
-        <v>0.20930000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>15</v>
-      </c>
-      <c r="D9">
-        <v>0.32590000000000002</v>
-      </c>
-      <c r="E9">
-        <v>200000</v>
-      </c>
-      <c r="F9">
-        <v>0.22109999999999999</v>
-      </c>
-      <c r="G9">
-        <v>0.1048</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>16</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>200000</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
